--- a/financial_models/opportunities/financial_companies/601166.SS_ddm.xlsx
+++ b/financial_models/opportunities/financial_companies/601166.SS_ddm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\financial_companies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21476B6-EAEB-4E25-9CA4-ED1BCCF6309B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A578BC9-35DF-4618-82E6-5907F5E87C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="262">
   <si>
     <t>Sales</t>
   </si>
@@ -932,12 +932,18 @@
   <si>
     <t>stage-2</t>
   </si>
+  <si>
+    <t>Instruction</t>
+  </si>
+  <si>
+    <t>Pre-tax Profit ROA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="16">
+  <numFmts count="17">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
@@ -954,6 +960,7 @@
     <numFmt numFmtId="176" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="177" formatCode="#,##0_);\(#,##0\);0;@"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
+    <numFmt numFmtId="179" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="45">
     <font>
@@ -1447,7 +1454,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="263">
+  <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2015,23 +2022,26 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2330,7 +2340,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:I45"/>
+  <dimension ref="A2:I46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -2448,13 +2458,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="257" t="s">
+      <c r="B12" s="261" t="s">
         <v>251</v>
       </c>
-      <c r="C12" s="257"/>
-      <c r="D12" s="257"/>
-      <c r="E12" s="257"/>
-      <c r="F12" s="257"/>
+      <c r="C12" s="261"/>
+      <c r="D12" s="261"/>
+      <c r="E12" s="261"/>
+      <c r="F12" s="261"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="34" t="str">
@@ -2552,7 +2562,7 @@
       <c r="E21" s="220">
         <v>3</v>
       </c>
-      <c r="F21" s="260" t="s">
+      <c r="F21" s="258" t="s">
         <v>244</v>
       </c>
     </row>
@@ -2659,10 +2669,10 @@
       <c r="D29" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="E29" s="262" t="s">
+      <c r="E29" s="260" t="s">
         <v>258</v>
       </c>
-      <c r="F29" s="262" t="s">
+      <c r="F29" s="260" t="s">
         <v>259</v>
       </c>
     </row>
@@ -2670,14 +2680,14 @@
       <c r="B30" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C30" s="261">
+      <c r="C30" s="259">
         <f>Past_EBITDA!G61</f>
         <v>1.06</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E30" s="259">
+      <c r="E30" s="257">
         <f>Past_EBITDA!C61</f>
         <v>1.06</v>
       </c>
@@ -2761,141 +2771,147 @@
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:6">
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-    </row>
-    <row r="38" spans="1:6" ht="13.9">
-      <c r="A38" s="132" t="s">
+    <row r="37" spans="1:6" ht="13.9">
+      <c r="A37" s="132" t="s">
         <v>245</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-    </row>
-    <row r="40" spans="1:6" ht="12.4">
-      <c r="B40" s="122" t="s">
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+    </row>
+    <row r="39" spans="1:6" ht="12.4">
+      <c r="B39" s="122" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="122" t="s">
+      <c r="C39" s="122" t="s">
         <v>103</v>
       </c>
-      <c r="D40" s="122" t="s">
+      <c r="D39" s="122" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="123" t="s">
+      <c r="E39" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="F40" s="123" t="s">
+      <c r="F39" s="123" t="s">
         <v>246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="12.75">
+      <c r="B40" s="90" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="100">
+        <f>DDM!C83</f>
+        <v>0.06</v>
+      </c>
+      <c r="D40" s="103">
+        <f>DDM!D83</f>
+        <v>30</v>
+      </c>
+      <c r="E40" s="97">
+        <f>DDM!E83</f>
+        <v>34.967067622606031</v>
+      </c>
+      <c r="F40" s="100">
+        <f>RATE(Holding_Period,Scenarios!$C$33,-E40,$C$19)</f>
+        <v>-0.1396276519141304</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="12.75">
       <c r="B41" s="90" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C41" s="100">
-        <f>DDM!C83</f>
-        <v>0.06</v>
+        <f>DDM!C84</f>
+        <v>0.05</v>
       </c>
       <c r="D41" s="103">
-        <f>DDM!D83</f>
+        <f>DDM!D84</f>
         <v>30</v>
       </c>
       <c r="E41" s="97">
-        <f>DDM!E83</f>
-        <v>34.967067622606031</v>
+        <f>DDM!E84</f>
+        <v>28.924149911288289</v>
       </c>
       <c r="F41" s="100">
         <f>RATE(Holding_Period,Scenarios!$C$33,-E41,$C$19)</f>
-        <v>-0.1396276519141304</v>
+        <v>-8.1342413063184155E-2</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="12.75">
       <c r="B42" s="90" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C42" s="100">
-        <f>DDM!C84</f>
-        <v>0.05</v>
+        <f>DDM!C85</f>
+        <v>0.03</v>
       </c>
       <c r="D42" s="103">
-        <f>DDM!D84</f>
+        <f>DDM!D85</f>
         <v>30</v>
       </c>
       <c r="E42" s="97">
-        <f>DDM!E84</f>
-        <v>28.924149911288289</v>
+        <f>DDM!E85</f>
+        <v>20.244158385425507</v>
       </c>
       <c r="F42" s="100">
         <f>RATE(Holding_Period,Scenarios!$C$33,-E42,$C$19)</f>
-        <v>-8.1342413063184155E-2</v>
+        <v>3.9920487093723284E-2</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="12.75">
       <c r="B43" s="90" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C43" s="100">
-        <f>DDM!C85</f>
-        <v>0.03</v>
+        <f>DDM!C86</f>
+        <v>0.01</v>
       </c>
       <c r="D43" s="103">
-        <f>DDM!D85</f>
+        <f>DDM!D86</f>
         <v>30</v>
       </c>
       <c r="E43" s="97">
-        <f>DDM!E85</f>
-        <v>20.244158385425507</v>
+        <f>DDM!E86</f>
+        <v>14.639564963717255</v>
       </c>
       <c r="F43" s="100">
         <f>RATE(Holding_Period,Scenarios!$C$33,-E43,$C$19)</f>
-        <v>3.9920487093723284E-2</v>
+        <v>0.16502717155019972</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="12.75">
       <c r="B44" s="90" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C44" s="100">
-        <f>DDM!C86</f>
-        <v>0.01</v>
+        <f>DDM!C87</f>
+        <v>0</v>
       </c>
       <c r="D44" s="103">
-        <f>DDM!D86</f>
+        <f>DDM!D87</f>
         <v>30</v>
       </c>
       <c r="E44" s="97">
-        <f>DDM!E86</f>
-        <v>14.639564963717255</v>
+        <f>DDM!E87</f>
+        <v>12.607966635404161</v>
       </c>
       <c r="F44" s="100">
         <f>RATE(Holding_Period,Scenarios!$C$33,-E44,$C$19)</f>
-        <v>0.16502717155019972</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="12.75">
-      <c r="B45" s="90" t="s">
-        <v>129</v>
-      </c>
-      <c r="C45" s="100">
-        <f>DDM!C87</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="103">
-        <f>DDM!D87</f>
-        <v>30</v>
-      </c>
-      <c r="E45" s="97">
-        <f>DDM!E87</f>
-        <v>12.607966635404161</v>
-      </c>
-      <c r="F45" s="100">
-        <f>RATE(Holding_Period,Scenarios!$C$33,-E45,$C$19)</f>
         <v>0.22810365128653981</v>
       </c>
+    </row>
+    <row r="46" spans="1:6" ht="13.9">
+      <c r="A46" s="132" t="s">
+        <v>260</v>
+      </c>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5256,7 +5272,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q768"/>
+  <dimension ref="A1:Q769"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
@@ -8782,233 +8798,289 @@
     </row>
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="49"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="53"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12"/>
-      <c r="I81" s="12"/>
-      <c r="J81" s="12"/>
-      <c r="K81" s="12"/>
-      <c r="L81" s="12"/>
-      <c r="M81" s="12"/>
-      <c r="N81" s="12"/>
-      <c r="O81" s="12"/>
-      <c r="P81" s="12"/>
-      <c r="Q81" s="12"/>
+      <c r="B81" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="C81" s="73">
+        <f>C12/C21</f>
+        <v>1.4539598690432663E-2</v>
+      </c>
+      <c r="D81" s="263"/>
+      <c r="E81" s="145"/>
+      <c r="F81" s="74"/>
+      <c r="G81" s="73">
+        <f>IF(G$4="","",G12/G21)</f>
+        <v>1.4026211522037995E-2</v>
+      </c>
+      <c r="H81" s="73">
+        <f t="shared" ref="H81:Q81" si="42">IF(H$4="","",H12/H21)</f>
+        <v>1.4305309752807697E-2</v>
+      </c>
+      <c r="I81" s="73">
+        <f t="shared" si="42"/>
+        <v>1.6703085714384378E-2</v>
+      </c>
+      <c r="J81" s="73">
+        <f t="shared" si="42"/>
+        <v>1.8854881725309611E-2</v>
+      </c>
+      <c r="K81" s="73">
+        <f t="shared" si="42"/>
+        <v>1.9251836838104889E-2</v>
+      </c>
+      <c r="L81" s="73">
+        <f t="shared" si="42"/>
+        <v>1.8523356976053087E-2</v>
+      </c>
+      <c r="M81" s="73">
+        <f t="shared" si="42"/>
+        <v>1.7032753610621044E-2</v>
+      </c>
+      <c r="N81" s="73">
+        <f t="shared" si="42"/>
+        <v>1.5633858524177469E-2</v>
+      </c>
+      <c r="O81" s="73">
+        <f t="shared" si="42"/>
+        <v>1.8839956982498057E-2</v>
+      </c>
+      <c r="P81" s="73">
+        <f t="shared" si="42"/>
+        <v>2.0394875898303036E-2</v>
+      </c>
+      <c r="Q81" s="73" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
     </row>
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
-      <c r="B82" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C82" s="41"/>
-      <c r="D82" s="43"/>
-      <c r="E82" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="F82" s="43"/>
-      <c r="G82" s="27"/>
-      <c r="H82" s="27"/>
-      <c r="I82" s="27"/>
-      <c r="J82" s="27"/>
-      <c r="K82" s="27"/>
-      <c r="L82" s="27"/>
-      <c r="M82" s="27"/>
-      <c r="N82" s="27"/>
-      <c r="O82" s="27"/>
-      <c r="P82" s="27"/>
-      <c r="Q82" s="27"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="49"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="12"/>
+      <c r="K82" s="12"/>
+      <c r="L82" s="12"/>
+      <c r="M82" s="12"/>
+      <c r="N82" s="12"/>
+      <c r="O82" s="12"/>
+      <c r="P82" s="12"/>
+      <c r="Q82" s="12"/>
     </row>
     <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
-      <c r="B83" s="128" t="s">
-        <v>57</v>
-      </c>
-      <c r="C83" s="129"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="140"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12"/>
-      <c r="I83" s="12"/>
-      <c r="J83" s="12"/>
-      <c r="K83" s="12"/>
-      <c r="L83" s="12"/>
-      <c r="M83" s="12"/>
-      <c r="N83" s="12"/>
-      <c r="O83" s="12"/>
-      <c r="P83" s="12"/>
-      <c r="Q83" s="12"/>
+      <c r="B83" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83" s="41"/>
+      <c r="D83" s="43"/>
+      <c r="E83" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F83" s="43"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="27"/>
+      <c r="I83" s="27"/>
+      <c r="J83" s="27"/>
+      <c r="K83" s="27"/>
+      <c r="L83" s="27"/>
+      <c r="M83" s="27"/>
+      <c r="N83" s="27"/>
+      <c r="O83" s="27"/>
+      <c r="P83" s="27"/>
+      <c r="Q83" s="27"/>
     </row>
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
-      <c r="B84" s="18" t="str">
-        <f>"After-tax Profit per share ("&amp;Market_currency&amp;")"</f>
-        <v>After-tax Profit per share (CNY)</v>
-      </c>
-      <c r="C84" s="127">
-        <f>C15*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>5.4586224746020449</v>
-      </c>
+      <c r="B84" s="128" t="s">
+        <v>57</v>
+      </c>
+      <c r="C84" s="129"/>
       <c r="D84" s="18"/>
       <c r="E84" s="140"/>
       <c r="F84" s="18"/>
-      <c r="G84" s="127">
-        <f t="shared" ref="G84:Q84" si="42">IF(G$4="","",G15*scaling_factor/Common_Shares*Exchange_Rate)</f>
-        <v>6.6173553593746677</v>
-      </c>
-      <c r="H84" s="127">
-        <f t="shared" si="42"/>
-        <v>6.6478738199797665</v>
-      </c>
-      <c r="I84" s="127">
-        <f t="shared" si="42"/>
-        <v>6.7361077920446659</v>
-      </c>
-      <c r="J84" s="127">
-        <f t="shared" si="42"/>
-        <v>7.2001905660095833</v>
-      </c>
-      <c r="K84" s="127">
-        <f t="shared" si="42"/>
-        <v>6.8335839477628442</v>
-      </c>
-      <c r="L84" s="127">
-        <f t="shared" si="42"/>
-        <v>5.9557690461941029</v>
-      </c>
-      <c r="M84" s="127">
-        <f t="shared" si="42"/>
-        <v>5.1439009759013636</v>
-      </c>
-      <c r="N84" s="127">
-        <f t="shared" si="42"/>
-        <v>4.4654669321028422</v>
-      </c>
-      <c r="O84" s="127">
-        <f t="shared" si="42"/>
-        <v>5.0342463177650627</v>
-      </c>
-      <c r="P84" s="127">
-        <f t="shared" si="42"/>
-        <v>4.5745439537608137</v>
-      </c>
-      <c r="Q84" s="127" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="12"/>
+      <c r="K84" s="12"/>
+      <c r="L84" s="12"/>
+      <c r="M84" s="12"/>
+      <c r="N84" s="12"/>
+      <c r="O84" s="12"/>
+      <c r="P84" s="12"/>
+      <c r="Q84" s="12"/>
     </row>
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
-      <c r="B85" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="C85" s="60">
-        <f>C84/Market_Price</f>
-        <v>0.2556731838221098</v>
+      <c r="B85" s="18" t="str">
+        <f>"After-tax Profit per share ("&amp;Market_currency&amp;")"</f>
+        <v>After-tax Profit per share (CNY)</v>
+      </c>
+      <c r="C85" s="127">
+        <f>C15*scaling_factor/Common_Shares*Exchange_Rate</f>
+        <v>5.4586224746020449</v>
       </c>
       <c r="D85" s="18"/>
       <c r="E85" s="140"/>
       <c r="F85" s="18"/>
-      <c r="G85" s="60">
-        <f t="shared" ref="G85" si="43">IF(G$4="","",G84/Market_Price)</f>
+      <c r="G85" s="127">
+        <f t="shared" ref="G85:Q85" si="43">IF(G$4="","",G15*scaling_factor/Common_Shares*Exchange_Rate)</f>
+        <v>6.6173553593746677</v>
+      </c>
+      <c r="H85" s="127">
+        <f t="shared" si="43"/>
+        <v>6.6478738199797665</v>
+      </c>
+      <c r="I85" s="127">
+        <f t="shared" si="43"/>
+        <v>6.7361077920446659</v>
+      </c>
+      <c r="J85" s="127">
+        <f t="shared" si="43"/>
+        <v>7.2001905660095833</v>
+      </c>
+      <c r="K85" s="127">
+        <f t="shared" si="43"/>
+        <v>6.8335839477628442</v>
+      </c>
+      <c r="L85" s="127">
+        <f t="shared" si="43"/>
+        <v>5.9557690461941029</v>
+      </c>
+      <c r="M85" s="127">
+        <f t="shared" si="43"/>
+        <v>5.1439009759013636</v>
+      </c>
+      <c r="N85" s="127">
+        <f t="shared" si="43"/>
+        <v>4.4654669321028422</v>
+      </c>
+      <c r="O85" s="127">
+        <f t="shared" si="43"/>
+        <v>5.0342463177650627</v>
+      </c>
+      <c r="P85" s="127">
+        <f t="shared" si="43"/>
+        <v>4.5745439537608137</v>
+      </c>
+      <c r="Q85" s="127" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A86" s="10"/>
+      <c r="B86" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" s="60">
+        <f>C85/Market_Price</f>
+        <v>0.2556731838221098</v>
+      </c>
+      <c r="D86" s="18"/>
+      <c r="E86" s="140"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="60">
+        <f t="shared" ref="G86" si="44">IF(G$4="","",G85/Market_Price)</f>
         <v>0.30994638685595632</v>
       </c>
-      <c r="H85" s="60">
-        <f t="shared" ref="H85" si="44">IF(H$4="","",H84/Market_Price)</f>
+      <c r="H86" s="60">
+        <f t="shared" ref="H86" si="45">IF(H$4="","",H85/Market_Price)</f>
         <v>0.31137582294987193</v>
       </c>
-      <c r="I85" s="60">
-        <f t="shared" ref="I85" si="45">IF(I$4="","",I84/Market_Price)</f>
+      <c r="I86" s="60">
+        <f t="shared" ref="I86" si="46">IF(I$4="","",I85/Market_Price)</f>
         <v>0.31550856168827474</v>
       </c>
-      <c r="J85" s="60">
-        <f t="shared" ref="J85" si="46">IF(J$4="","",J84/Market_Price)</f>
+      <c r="J86" s="60">
+        <f t="shared" ref="J86" si="47">IF(J$4="","",J85/Market_Price)</f>
         <v>0.33724545976625681</v>
       </c>
-      <c r="K85" s="60">
-        <f t="shared" ref="K85" si="47">IF(K$4="","",K84/Market_Price)</f>
+      <c r="K86" s="60">
+        <f t="shared" ref="K86" si="48">IF(K$4="","",K85/Market_Price)</f>
         <v>0.3200741895907655</v>
       </c>
-      <c r="L85" s="60">
-        <f t="shared" ref="L85" si="48">IF(L$4="","",L84/Market_Price)</f>
+      <c r="L86" s="60">
+        <f t="shared" ref="L86" si="49">IF(L$4="","",L85/Market_Price)</f>
         <v>0.27895873752665584</v>
       </c>
-      <c r="M85" s="60">
-        <f t="shared" ref="M85" si="49">IF(M$4="","",M84/Market_Price)</f>
+      <c r="M86" s="60">
+        <f t="shared" ref="M86" si="50">IF(M$4="","",M85/Market_Price)</f>
         <v>0.24093213001879921</v>
       </c>
-      <c r="N85" s="60">
-        <f t="shared" ref="N85" si="50">IF(N$4="","",N84/Market_Price)</f>
+      <c r="N86" s="60">
+        <f t="shared" ref="N86" si="51">IF(N$4="","",N85/Market_Price)</f>
         <v>0.20915535981746333</v>
       </c>
-      <c r="O85" s="60">
-        <f t="shared" ref="O85" si="51">IF(O$4="","",O84/Market_Price)</f>
+      <c r="O86" s="60">
+        <f t="shared" ref="O86" si="52">IF(O$4="","",O85/Market_Price)</f>
         <v>0.23579608045737996</v>
       </c>
-      <c r="P85" s="60">
-        <f t="shared" ref="P85" si="52">IF(P$4="","",P84/Market_Price)</f>
+      <c r="P86" s="60">
+        <f t="shared" ref="P86" si="53">IF(P$4="","",P85/Market_Price)</f>
         <v>0.2142643538061271</v>
       </c>
-      <c r="Q85" s="60" t="str">
-        <f t="shared" ref="Q85" si="53">IF(Q$4="","",Q84/Market_Price)</f>
+      <c r="Q86" s="60" t="str">
+        <f t="shared" ref="Q86" si="54">IF(Q$4="","",Q85/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B86" s="2" t="s">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B87" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C86" s="120"/>
-      <c r="G86" s="15">
+      <c r="C87" s="120"/>
+      <c r="G87" s="15">
         <f>IF(G$4="","",(Data!C43*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.17471361569971058</v>
       </c>
-      <c r="H86" s="15">
+      <c r="H87" s="15">
         <f>IF(H$4="","",(Data!D43*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.17508112056297279</v>
       </c>
-      <c r="I86" s="15">
+      <c r="I87" s="15">
         <f>IF(I$4="","",(Data!E43*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.20835947505223901</v>
       </c>
-      <c r="J86" s="15">
+      <c r="J87" s="15">
         <f>IF(J$4="","",(Data!F43*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.18897415717292254</v>
       </c>
-      <c r="K86" s="15">
+      <c r="K87" s="15">
         <f>IF(K$4="","",(Data!G43*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.15259568497208853</v>
       </c>
-      <c r="L86" s="15">
+      <c r="L87" s="15">
         <f>IF(L$4="","",(Data!H43*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.15038840116145225</v>
       </c>
-      <c r="M86" s="15">
+      <c r="M87" s="15">
         <f>IF(M$4="","",(Data!I43*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.13808487945088815</v>
       </c>
-      <c r="N86" s="15">
+      <c r="N87" s="15">
         <f>IF(N$4="","",(Data!J43*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.13017112441990411</v>
       </c>
-      <c r="O86" s="15">
+      <c r="O87" s="15">
         <f>IF(O$4="","",(Data!K43*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.12248734175734184</v>
       </c>
-      <c r="P86" s="15">
+      <c r="P87" s="15">
         <f>IF(P$4="","",(Data!L43*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.11419706333884375</v>
       </c>
-      <c r="Q86" s="15" t="str">
+      <c r="Q87" s="15" t="str">
         <f>IF(Q$4="","",(Data!M43*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="88" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="89" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="90" spans="1:17" ht="15.75" customHeight="1"/>
@@ -9690,6 +9762,7 @@
     <row r="766" ht="15.75" customHeight="1"/>
     <row r="767" ht="15.75" customHeight="1"/>
     <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q12 G14:Q16">
@@ -14580,7 +14653,7 @@
       <c r="C4" s="226">
         <v>2</v>
       </c>
-      <c r="D4" s="258" t="str">
+      <c r="D4" s="262" t="str">
         <f>"DDM Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -14590,16 +14663,16 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DDM Model Inputs for 601166.SS – 兴业银行: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" s="222"/>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="114" t="s">
@@ -14609,10 +14682,10 @@
         <f>DDM!C3&amp;" "&amp;Reporting_currency</f>
         <v>1000000 CNY</v>
       </c>
-      <c r="D6" s="258"/>
-      <c r="E6" s="258"/>
-      <c r="F6" s="258"/>
-      <c r="G6" s="258"/>
+      <c r="D6" s="262"/>
+      <c r="E6" s="262"/>
+      <c r="F6" s="262"/>
+      <c r="G6" s="262"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="71" t="s">
@@ -14622,10 +14695,10 @@
         <f>Past_EBITDA!G6</f>
         <v>405725</v>
       </c>
-      <c r="D7" s="258"/>
-      <c r="E7" s="258"/>
-      <c r="F7" s="258"/>
-      <c r="G7" s="258"/>
+      <c r="D7" s="262"/>
+      <c r="E7" s="262"/>
+      <c r="F7" s="262"/>
+      <c r="G7" s="262"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="71" t="s">
@@ -14635,26 +14708,26 @@
         <f>Past_EBITDA!C6</f>
         <v>405725</v>
       </c>
-      <c r="D8" s="258"/>
-      <c r="E8" s="258"/>
-      <c r="F8" s="258"/>
-      <c r="G8" s="258"/>
+      <c r="D8" s="262"/>
+      <c r="E8" s="262"/>
+      <c r="F8" s="262"/>
+      <c r="G8" s="262"/>
     </row>
     <row r="9" spans="2:7">
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
+      <c r="D9" s="262"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="262"/>
     </row>
     <row r="10" spans="2:7" ht="13.15">
       <c r="B10" s="114" t="s">
         <v>90</v>
       </c>
       <c r="C10" s="225"/>
-      <c r="D10" s="258"/>
-      <c r="E10" s="258"/>
-      <c r="F10" s="258"/>
-      <c r="G10" s="258"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="262"/>
+      <c r="F10" s="262"/>
+      <c r="G10" s="262"/>
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="85" t="s">
@@ -14664,10 +14737,10 @@
         <f ca="1">(Past_EBITDA!G4/OFFSET(Past_EBITDA!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>2.2691868219390177E-2</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
+      <c r="D11" s="262"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="262"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="104" t="s">
@@ -14677,24 +14750,24 @@
         <f ca="1">(Past_EBITDA!G9/OFFSET(Past_EBITDA!G9, 0, $C$4))^(1/$C$4) - 1</f>
         <v>7.156840923368879E-3</v>
       </c>
-      <c r="D12" s="258"/>
-      <c r="E12" s="258"/>
-      <c r="F12" s="258"/>
-      <c r="G12" s="258"/>
+      <c r="D12" s="262"/>
+      <c r="E12" s="262"/>
+      <c r="F12" s="262"/>
+      <c r="G12" s="262"/>
     </row>
     <row r="13" spans="2:7">
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="258"/>
-      <c r="G13" s="258"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="262"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="262"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="71"/>
       <c r="C14" s="150"/>
-      <c r="D14" s="258"/>
-      <c r="E14" s="258"/>
-      <c r="F14" s="258"/>
-      <c r="G14" s="258"/>
+      <c r="D14" s="262"/>
+      <c r="E14" s="262"/>
+      <c r="F14" s="262"/>
+      <c r="G14" s="262"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="26" t="s">
